--- a/Llamen a Dios/Resources/Plantilla Cierre de Caja.xlsx
+++ b/Llamen a Dios/Resources/Plantilla Cierre de Caja.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonku\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1CA807-CCE0-41E0-8ECB-1E80C68256D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F145A137-6F8C-4875-A72D-076B493D5589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{3E226D24-DF79-48D7-B4DA-EDFDB0A00578}"/>
   </bookViews>
@@ -69,19 +69,19 @@
     <t>PAN DE PARÍS C.A</t>
   </si>
   <si>
-    <t>Generado: 03/07/2026 05:26 PM</t>
-  </si>
-  <si>
     <t>Por:</t>
   </si>
   <si>
-    <t>Direccion:</t>
-  </si>
-  <si>
     <t>Movimientos de Productos</t>
   </si>
   <si>
     <t xml:space="preserve">Generado: </t>
+  </si>
+  <si>
+    <t>Direccion: Av Jóvito Villalba, 6316, Nueva Esparta</t>
+  </si>
+  <si>
+    <t>Direccion:  Av Jóvito Villalba, 6316, Nueva Esparta</t>
   </si>
 </sst>
 </file>
@@ -170,7 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -181,28 +181,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -296,8 +293,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>179711</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1292231</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
@@ -658,125 +655,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7FCEFA-00B3-498A-9D84-5C02412A1246}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.109375" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="10" t="s">
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="9"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="7"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
+    <mergeCell ref="C7:E7"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9431875D-9F75-4D8B-B893-DE45FBD004C7}">
-  <dimension ref="A2:D12"/>
+  <dimension ref="A2:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
     <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C2" s="8" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C3" s="11" t="s">
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="11"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C4" s="8" t="s">
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -790,20 +805,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C4:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Llamen a Dios/Resources/Plantilla Cierre de Caja.xlsx
+++ b/Llamen a Dios/Resources/Plantilla Cierre de Caja.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonku\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F145A137-6F8C-4875-A72D-076B493D5589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E070648-8CF1-46FB-A62E-E392BB038D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{3E226D24-DF79-48D7-B4DA-EDFDB0A00578}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3E226D24-DF79-48D7-B4DA-EDFDB0A00578}"/>
   </bookViews>
   <sheets>
     <sheet name="Cierre de Caja" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>REPORTE DE CIERRE DE CAJA</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Total Generado</t>
   </si>
   <si>
-    <t>Rif. J-XXXXXXXXX</t>
-  </si>
-  <si>
     <t>PAN DE PARÍS C.A</t>
   </si>
   <si>
@@ -82,6 +79,15 @@
   </si>
   <si>
     <t>Direccion:  Av Jóvito Villalba, 6316, Nueva Esparta</t>
+  </si>
+  <si>
+    <t>Rif. J-30018877-9</t>
+  </si>
+  <si>
+    <t>Cost. Produccion</t>
+  </si>
+  <si>
+    <t>Utilidades</t>
   </si>
 </sst>
 </file>
@@ -131,7 +137,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,6 +162,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -170,7 +182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -178,33 +190,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="40% - Énfasis3" xfId="1" builtinId="39"/>
@@ -238,8 +256,8 @@
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1534111</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>132031</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -293,8 +311,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1292231</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>446411</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
@@ -655,12 +673,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7FCEFA-00B3-498A-9D84-5C02412A1246}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
     <col min="2" max="2" width="19.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -671,67 +689,903 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="9"/>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D4" s="8" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C6" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="C11" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="6"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="14"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="4"/>
+      <c r="B122" s="4"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="4"/>
+      <c r="B124" s="4"/>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="4"/>
+      <c r="B125" s="4"/>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="4"/>
+      <c r="B126" s="4"/>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="4"/>
+      <c r="B127" s="4"/>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="4"/>
+      <c r="B128" s="4"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="4"/>
+      <c r="B129" s="4"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="4"/>
+      <c r="B130" s="4"/>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="4"/>
+      <c r="B131" s="4"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="4"/>
+      <c r="B132" s="4"/>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="4"/>
+      <c r="B133" s="4"/>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="4"/>
+      <c r="B134" s="4"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="4"/>
+      <c r="B135" s="4"/>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="4"/>
+      <c r="B136" s="4"/>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="4"/>
+      <c r="B137" s="4"/>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="4"/>
+      <c r="B138" s="4"/>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="4"/>
+      <c r="B139" s="4"/>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="4"/>
+      <c r="B140" s="4"/>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="4"/>
+      <c r="B141" s="4"/>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="4"/>
+      <c r="B142" s="4"/>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="4"/>
+      <c r="B143" s="4"/>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="4"/>
+      <c r="B145" s="4"/>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="4"/>
+      <c r="B146" s="4"/>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="4"/>
+      <c r="B147" s="4"/>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="4"/>
+      <c r="B149" s="4"/>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="4"/>
+      <c r="B150" s="4"/>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="4"/>
+      <c r="B152" s="4"/>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="4"/>
+      <c r="B153" s="4"/>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="4"/>
+      <c r="B154" s="4"/>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="4"/>
+      <c r="B155" s="4"/>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="4"/>
+      <c r="B156" s="4"/>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="4"/>
+      <c r="B157" s="4"/>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="4"/>
+      <c r="B158" s="4"/>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="4"/>
+      <c r="B159" s="4"/>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="4"/>
+      <c r="B160" s="4"/>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="4"/>
+      <c r="B161" s="4"/>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="4"/>
+      <c r="B162" s="4"/>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="4"/>
+      <c r="B163" s="4"/>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="4"/>
+      <c r="B164" s="4"/>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="4"/>
+      <c r="B165" s="4"/>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="4"/>
+      <c r="B166" s="4"/>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="4"/>
+      <c r="B167" s="4"/>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="4"/>
+      <c r="B168" s="4"/>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="4"/>
+      <c r="B169" s="4"/>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="4"/>
+      <c r="B170" s="4"/>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="4"/>
+      <c r="B171" s="4"/>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="4"/>
+      <c r="B172" s="4"/>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="4"/>
+      <c r="B173" s="4"/>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="4"/>
+      <c r="B174" s="4"/>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="4"/>
+      <c r="B175" s="4"/>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="4"/>
+      <c r="B176" s="4"/>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="4"/>
+      <c r="B177" s="4"/>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="4"/>
+      <c r="B178" s="4"/>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="4"/>
+      <c r="B179" s="4"/>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="4"/>
+      <c r="B180" s="4"/>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="4"/>
+      <c r="B181" s="4"/>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="4"/>
+      <c r="B182" s="4"/>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="4"/>
+      <c r="B183" s="4"/>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="4"/>
+      <c r="B184" s="4"/>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="4"/>
+      <c r="B185" s="4"/>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="4"/>
+      <c r="B186" s="4"/>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="4"/>
+      <c r="B187" s="4"/>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="4"/>
+      <c r="B188" s="4"/>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="4"/>
+      <c r="B189" s="4"/>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="4"/>
+      <c r="B190" s="4"/>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="4"/>
+      <c r="B191" s="4"/>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="4"/>
+      <c r="B192" s="4"/>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="4"/>
+      <c r="B193" s="4"/>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="4"/>
+      <c r="B194" s="4"/>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="4"/>
+      <c r="B195" s="4"/>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="4"/>
+      <c r="B196" s="4"/>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="4"/>
+      <c r="B197" s="4"/>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="4"/>
+      <c r="B198" s="4"/>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="4"/>
+      <c r="B199" s="4"/>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="4"/>
+      <c r="B200" s="4"/>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="4"/>
+      <c r="B201" s="4"/>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="4"/>
+      <c r="B202" s="4"/>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="4"/>
+      <c r="B203" s="4"/>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="4"/>
+      <c r="B204" s="4"/>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="4"/>
+      <c r="B205" s="4"/>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="4"/>
+      <c r="B206" s="4"/>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="4"/>
+      <c r="B207" s="4"/>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="4"/>
+      <c r="B208" s="4"/>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="4"/>
+      <c r="B209" s="4"/>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="4"/>
+      <c r="B210" s="4"/>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="4"/>
+      <c r="B211" s="4"/>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="4"/>
+      <c r="B212" s="4"/>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="4"/>
+      <c r="B213" s="4"/>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="4"/>
+      <c r="B214" s="4"/>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="4"/>
+      <c r="B215" s="4"/>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="4"/>
+      <c r="B216" s="4"/>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="4"/>
+      <c r="B217" s="4"/>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="4"/>
+      <c r="B218" s="4"/>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="4"/>
+      <c r="B219" s="4"/>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="4"/>
+      <c r="B220" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -741,55 +1595,55 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9431875D-9F75-4D8B-B893-DE45FBD004C7}">
-  <dimension ref="A2:E12"/>
+  <dimension ref="A2:E44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="9"/>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D3" s="8" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C6" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -806,19 +1660,209 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C4:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
